--- a/MaterialApi/Data/IGQC_Data.xlsx
+++ b/MaterialApi/Data/IGQC_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\BDL\MaterialApi\MaterialApi\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3106B679-4D52-40FE-AA67-3FB03DEFEF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C43672-3DCD-4416-857A-2995EF0982F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{EDCD305C-838E-4280-9A35-687393AE6FEC}"/>
+    <workbookView xWindow="4920" yWindow="2655" windowWidth="21600" windowHeight="11385" xr2:uid="{EDCD305C-838E-4280-9A35-687393AE6FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>PO</t>
   </si>
@@ -97,15 +97,6 @@
   </si>
   <si>
     <t>Dimensional Sample Consumed</t>
-  </si>
-  <si>
-    <t>Chemical Expected Result</t>
-  </si>
-  <si>
-    <t>Mechanical Expected Result</t>
-  </si>
-  <si>
-    <t>Dimensional Expected Result</t>
   </si>
 </sst>
 </file>
@@ -511,7 +502,7 @@
     <col min="27" max="27" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -584,15 +575,9 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
